--- a/03_Outputs/Cartama/09_Salud/salud.xlsx
+++ b/03_Outputs/Cartama/09_Salud/salud.xlsx
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="E13" s="7">
-        <v>14.7408786905713</v>
+        <v>14.7408786905712</v>
       </c>
       <c r="F13" s="9">
-        <v>2.67744209761243</v>
+        <v>2.67744209761242</v>
       </c>
       <c r="G13" s="11">
         <v>7.84034152235333</v>
